--- a/reports.xlsx
+++ b/reports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ts1\Desktop\ReportsPortal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD42494B-53E9-4CA8-A20C-E561461F6AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46539865-1690-4616-A744-234A429A1BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="63">
   <si>
     <t>دمشق</t>
   </si>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>SC</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQCOg4diczeJRbu1ZCX_dPmTAZUh9MFMtphL3cxv_x5xSzA?e=ZYxsYc</t>
   </si>
 </sst>
 </file>
@@ -295,7 +298,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -322,9 +325,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -618,7 +618,7 @@
     <col min="5" max="5" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.7109375" style="2" customWidth="1"/>
     <col min="7" max="7" width="42.28515625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="134" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="167.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.28515625" customWidth="1"/>
     <col min="15" max="15" width="13.140625" customWidth="1"/>
   </cols>
@@ -724,7 +724,7 @@
         <v>17</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -980,7 +980,7 @@
       <c r="F14" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H14" s="9" t="s">
@@ -1214,23 +1214,23 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H6" r:id="rId1" xr:uid="{43466B94-1F9B-47C9-A8CA-10A9A3D8BD75}"/>
-    <hyperlink ref="H4" r:id="rId2" xr:uid="{D21B5085-DBBD-41E8-8F68-DA302CB82310}"/>
-    <hyperlink ref="H3" r:id="rId3" xr:uid="{52B335DB-3034-4991-9796-B761C3D3B2A8}"/>
-    <hyperlink ref="H2" r:id="rId4" xr:uid="{336B8B20-D660-4A64-B0E9-C055FAAC3D70}"/>
-    <hyperlink ref="H7" r:id="rId5" xr:uid="{8B7E5547-9333-4D0B-BE4B-80B5FAAAEBB1}"/>
-    <hyperlink ref="H8" r:id="rId6" xr:uid="{154A14F9-6CD6-42FA-99D5-C20544FA3FB7}"/>
-    <hyperlink ref="H5" r:id="rId7" xr:uid="{8CAAE066-D0FE-4559-A964-436D0E549866}"/>
-    <hyperlink ref="H9" r:id="rId8" xr:uid="{B24A7CFC-1CEB-49D3-BC3A-A83471D21440}"/>
-    <hyperlink ref="H10" r:id="rId9" xr:uid="{958C80E8-B475-4850-A23A-216CD5ABA607}"/>
-    <hyperlink ref="H11" r:id="rId10" xr:uid="{0538F384-0865-4940-950F-EDE8773162F7}"/>
-    <hyperlink ref="H12" r:id="rId11" xr:uid="{76EB26DC-3ECA-4FD8-9E3E-BEAAA5E6C0C2}"/>
-    <hyperlink ref="H13" r:id="rId12" xr:uid="{FF14D42D-7476-47E6-8514-A622A5E55AEF}"/>
-    <hyperlink ref="H14" r:id="rId13" xr:uid="{8AA56A44-FA9F-472A-9BF0-B0F6B4D1CDDD}"/>
-    <hyperlink ref="H16" r:id="rId14" xr:uid="{A3282F6C-7406-4B2F-920C-C2C5D9A52467}"/>
-    <hyperlink ref="H17" r:id="rId15" xr:uid="{6729F0E1-5C17-45FA-ACC5-EE1A32F1BED3}"/>
-    <hyperlink ref="H18" r:id="rId16" xr:uid="{117A0F63-0BDF-4CB1-9D76-F1FAE20679D5}"/>
-    <hyperlink ref="H19" r:id="rId17" xr:uid="{E3BE19CF-AD72-4402-896D-C4066BA89802}"/>
-    <hyperlink ref="H20" r:id="rId18" xr:uid="{57B20AE8-45EB-4AA6-8DB4-0853701C8AC1}"/>
+    <hyperlink ref="H3" r:id="rId2" xr:uid="{52B335DB-3034-4991-9796-B761C3D3B2A8}"/>
+    <hyperlink ref="H2" r:id="rId3" xr:uid="{336B8B20-D660-4A64-B0E9-C055FAAC3D70}"/>
+    <hyperlink ref="H7" r:id="rId4" xr:uid="{8B7E5547-9333-4D0B-BE4B-80B5FAAAEBB1}"/>
+    <hyperlink ref="H8" r:id="rId5" xr:uid="{154A14F9-6CD6-42FA-99D5-C20544FA3FB7}"/>
+    <hyperlink ref="H5" r:id="rId6" xr:uid="{8CAAE066-D0FE-4559-A964-436D0E549866}"/>
+    <hyperlink ref="H9" r:id="rId7" xr:uid="{B24A7CFC-1CEB-49D3-BC3A-A83471D21440}"/>
+    <hyperlink ref="H10" r:id="rId8" xr:uid="{958C80E8-B475-4850-A23A-216CD5ABA607}"/>
+    <hyperlink ref="H11" r:id="rId9" xr:uid="{0538F384-0865-4940-950F-EDE8773162F7}"/>
+    <hyperlink ref="H12" r:id="rId10" xr:uid="{76EB26DC-3ECA-4FD8-9E3E-BEAAA5E6C0C2}"/>
+    <hyperlink ref="H13" r:id="rId11" xr:uid="{FF14D42D-7476-47E6-8514-A622A5E55AEF}"/>
+    <hyperlink ref="H14" r:id="rId12" xr:uid="{8AA56A44-FA9F-472A-9BF0-B0F6B4D1CDDD}"/>
+    <hyperlink ref="H16" r:id="rId13" xr:uid="{A3282F6C-7406-4B2F-920C-C2C5D9A52467}"/>
+    <hyperlink ref="H17" r:id="rId14" xr:uid="{6729F0E1-5C17-45FA-ACC5-EE1A32F1BED3}"/>
+    <hyperlink ref="H18" r:id="rId15" xr:uid="{117A0F63-0BDF-4CB1-9D76-F1FAE20679D5}"/>
+    <hyperlink ref="H19" r:id="rId16" xr:uid="{E3BE19CF-AD72-4402-896D-C4066BA89802}"/>
+    <hyperlink ref="H20" r:id="rId17" xr:uid="{57B20AE8-45EB-4AA6-8DB4-0853701C8AC1}"/>
+    <hyperlink ref="H4" r:id="rId18" xr:uid="{C4E0C6BA-B5C8-4F46-9BD0-107BEFD28C6A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId19"/>

--- a/reports.xlsx
+++ b/reports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ts1\Desktop\ReportsPortal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46539865-1690-4616-A744-234A429A1BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1077311A-E14D-4EF6-AEEA-2BD46E092CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="67">
   <si>
     <t>دمشق</t>
   </si>
@@ -225,6 +225,18 @@
   </si>
   <si>
     <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQCOg4diczeJRbu1ZCX_dPmTAZUh9MFMtphL3cxv_x5xSzA?e=ZYxsYc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وكيل </t>
+  </si>
+  <si>
+    <t>بيزوكاند</t>
+  </si>
+  <si>
+    <t>محافظة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">انتاج </t>
   </si>
 </sst>
 </file>
@@ -657,7 +669,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>16</v>
@@ -683,7 +695,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>0</v>
@@ -709,7 +721,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>0</v>
@@ -735,7 +747,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>16</v>
@@ -761,7 +773,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>15</v>
@@ -787,7 +799,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>16</v>
@@ -813,7 +825,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>16</v>
@@ -839,7 +851,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>16</v>
@@ -865,7 +877,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>16</v>
@@ -891,7 +903,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>16</v>
@@ -969,7 +981,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>16</v>
@@ -1021,7 +1033,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>16</v>

--- a/reports.xlsx
+++ b/reports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ts1\Desktop\ReportsPortal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1077311A-E14D-4EF6-AEEA-2BD46E092CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02AD152D-8E73-4A12-B78D-1AD502055048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31065" yWindow="1425" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="66">
   <si>
     <t>دمشق</t>
   </si>
@@ -213,9 +213,6 @@
   </si>
   <si>
     <t xml:space="preserve">تسويق </t>
-  </si>
-  <si>
-    <t>حالة الرف</t>
   </si>
   <si>
     <t xml:space="preserve">ادارة </t>
@@ -695,7 +692,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>0</v>
@@ -721,7 +718,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>0</v>
@@ -736,7 +733,7 @@
         <v>17</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -747,7 +744,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>16</v>
@@ -773,7 +770,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>15</v>
@@ -825,7 +822,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>16</v>
@@ -851,7 +848,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>16</v>
@@ -877,7 +874,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>16</v>
@@ -903,7 +900,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>16</v>
@@ -981,7 +978,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>16</v>
@@ -1033,13 +1030,13 @@
         <v>2</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>48</v>
@@ -1091,7 +1088,7 @@
         <v>52</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>52</v>
@@ -1117,7 +1114,7 @@
         <v>54</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>54</v>
@@ -1137,7 +1134,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>0</v>

--- a/reports.xlsx
+++ b/reports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ts1\Desktop\ReportsPortal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02AD152D-8E73-4A12-B78D-1AD502055048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B11DC7-F831-4597-AA34-B150CE8E4656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31065" yWindow="1425" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="71">
   <si>
     <t>دمشق</t>
   </si>
@@ -65,9 +65,6 @@
     <t>مبيعات</t>
   </si>
   <si>
-    <t>شهري</t>
-  </si>
-  <si>
     <t>حلب</t>
   </si>
   <si>
@@ -234,6 +231,24 @@
   </si>
   <si>
     <t xml:space="preserve">انتاج </t>
+  </si>
+  <si>
+    <t>‪ميكوبروجيل- دراسة تقنية 14-4-2026</t>
+  </si>
+  <si>
+    <t>‪ميكوبروجيل</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQB3gyaMCKxXS7vvHpbhVPpwAX0y7pfVtRp2DlrlMNUpTTs?e=JYvCyW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محافظات / مناطق </t>
+  </si>
+  <si>
+    <t>متابعة حالة المستحضر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">متابعة حالة المستحضر </t>
   </si>
 </sst>
 </file>
@@ -637,7 +652,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>2</v>
@@ -666,22 +681,22 @@
         <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="F2" s="5" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -692,7 +707,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>0</v>
@@ -701,13 +716,13 @@
         <v>8</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -718,7 +733,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>0</v>
@@ -727,13 +742,13 @@
         <v>8</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -744,22 +759,22 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>29</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -770,22 +785,22 @@
         <v>3</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -796,22 +811,22 @@
         <v>3</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>22</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -822,22 +837,22 @@
         <v>3</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -848,22 +863,22 @@
         <v>3</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -874,22 +889,22 @@
         <v>3</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -900,22 +915,22 @@
         <v>3</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>0</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -926,22 +941,22 @@
         <v>3</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -952,22 +967,22 @@
         <v>3</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -978,22 +993,22 @@
         <v>3</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1004,22 +1019,22 @@
         <v>2</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1030,22 +1045,22 @@
         <v>2</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1056,22 +1071,22 @@
         <v>2025</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F17" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="H17" s="9" t="s">
         <v>49</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1079,25 +1094,25 @@
         <v>2026</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1105,25 +1120,25 @@
         <v>2026</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1134,33 +1149,49 @@
         <v>3</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
+      <c r="A21" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B21" s="8">
+        <v>3</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
@@ -1240,8 +1271,9 @@
     <hyperlink ref="H19" r:id="rId16" xr:uid="{E3BE19CF-AD72-4402-896D-C4066BA89802}"/>
     <hyperlink ref="H20" r:id="rId17" xr:uid="{57B20AE8-45EB-4AA6-8DB4-0853701C8AC1}"/>
     <hyperlink ref="H4" r:id="rId18" xr:uid="{C4E0C6BA-B5C8-4F46-9BD0-107BEFD28C6A}"/>
+    <hyperlink ref="H21" r:id="rId19" xr:uid="{5EC65BAA-9064-428C-A5E9-3941F6C86E3C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId19"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId20"/>
 </worksheet>
 </file>
--- a/reports.xlsx
+++ b/reports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ts1\Desktop\ReportsPortal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B11DC7-F831-4597-AA34-B150CE8E4656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F449F7D2-ACEC-43BB-B077-63BD32B3B150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="73">
   <si>
     <t>دمشق</t>
   </si>
@@ -249,6 +249,12 @@
   </si>
   <si>
     <t xml:space="preserve">متابعة حالة المستحضر </t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQB-ykM4tRcqQI-QOoQc7koNAaBuqgpHAa4g_MiD3xObLYE?e=CRuaKO</t>
+  </si>
+  <si>
+    <t>بيوتي سكين</t>
   </si>
 </sst>
 </file>
@@ -1194,14 +1200,30 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
+      <c r="A22" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B22" s="8">
+        <v>3</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
@@ -1272,8 +1294,9 @@
     <hyperlink ref="H20" r:id="rId17" xr:uid="{57B20AE8-45EB-4AA6-8DB4-0853701C8AC1}"/>
     <hyperlink ref="H4" r:id="rId18" xr:uid="{C4E0C6BA-B5C8-4F46-9BD0-107BEFD28C6A}"/>
     <hyperlink ref="H21" r:id="rId19" xr:uid="{5EC65BAA-9064-428C-A5E9-3941F6C86E3C}"/>
+    <hyperlink ref="H22" r:id="rId20" xr:uid="{84A053E2-0209-425A-8A4E-B07290100CD5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId20"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId21"/>
 </worksheet>
 </file>
--- a/reports.xlsx
+++ b/reports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ts1\Desktop\ReportsPortal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F449F7D2-ACEC-43BB-B077-63BD32B3B150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87926D59-0272-4E9D-905B-C83E04929DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="84">
   <si>
     <t>دمشق</t>
   </si>
@@ -245,16 +245,49 @@
     <t xml:space="preserve">محافظات / مناطق </t>
   </si>
   <si>
-    <t>متابعة حالة المستحضر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">متابعة حالة المستحضر </t>
-  </si>
-  <si>
     <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQB-ykM4tRcqQI-QOoQc7koNAaBuqgpHAa4g_MiD3xObLYE?e=CRuaKO</t>
   </si>
   <si>
     <t>بيوتي سكين</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/Ultramedica-ForecastingAndAccurate/IQCfmlQwAJvQR6-B7hbRFo30AT7h4lq8clrGRLEEW_J2_cg?e=fIvWd4</t>
+  </si>
+  <si>
+    <t>Action Plan- April 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مبيعات </t>
+  </si>
+  <si>
+    <t>Forecasting April 2026</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/Ultramedica-ForecastingAndAccurate/IQBI-xz3OJdLSrjg0bkt_tpBAZ9HmPDj5FJY-maQZTQNQmo?e=MfZohG</t>
+  </si>
+  <si>
+    <t>Action Plan- Mar 2026</t>
+  </si>
+  <si>
+    <t>Forecasting Mar 2026</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/Ultramedica-ForecastingAndAccurate/IQA-AYJzC5uBSowSPIv64X6hARSgA7vh75Sy51D1KTfxL0Y?e=9JVido</t>
+  </si>
+  <si>
+    <t>Forecast Accuracy Mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مشترك </t>
+  </si>
+  <si>
+    <t>Forecast Accuracy Feb</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/Ultramedica-ForecastingAndAccurate/IQDRy5dV--zJR6EbOw8N521nAfJf0ii8wk9qLEXrwnWp72k?e=A2DaDl</t>
+  </si>
+  <si>
+    <t>Forecasting Feb 2026</t>
   </si>
 </sst>
 </file>
@@ -638,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2460"/>
+  <dimension ref="A1:O2478"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="2" customWidth="1"/>
@@ -693,10 +726,10 @@
         <v>15</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>20</v>
@@ -823,10 +856,10 @@
         <v>15</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>70</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>23</v>
@@ -1187,10 +1220,10 @@
         <v>68</v>
       </c>
       <c r="E21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>65</v>
@@ -1207,70 +1240,314 @@
         <v>3</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>68</v>
       </c>
       <c r="E22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="G22" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G22" s="8" t="s">
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="8">
+        <v>4</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G23" t="s">
         <v>72</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H23" s="9" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-    </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
+      <c r="A24" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="8">
+        <v>3</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2460" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F2460" s="3"/>
-      <c r="G2460" s="3"/>
-      <c r="H2460" s="3"/>
-      <c r="I2460" s="1"/>
-      <c r="J2460" s="1"/>
-      <c r="K2460" s="1"/>
-      <c r="L2460" s="1"/>
-      <c r="M2460" s="1"/>
-      <c r="N2460" s="1"/>
-      <c r="O2460" s="1"/>
+      <c r="A25" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B25" s="8">
+        <v>3</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B26" s="8">
+        <v>3</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="9"/>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="9"/>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="9"/>
+    </row>
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="9"/>
+    </row>
+    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="9"/>
+    </row>
+    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="9"/>
+    </row>
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="5"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="9"/>
+    </row>
+    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="9"/>
+    </row>
+    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="9"/>
+    </row>
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="5"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="9"/>
+    </row>
+    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="9"/>
+    </row>
+    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="5"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="9"/>
+    </row>
+    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="9"/>
+    </row>
+    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="9"/>
+    </row>
+    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+    </row>
+    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="8"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+    </row>
+    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+    </row>
+    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2478" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F2478" s="3"/>
+      <c r="G2478" s="3"/>
+      <c r="H2478" s="3"/>
+      <c r="I2478" s="1"/>
+      <c r="J2478" s="1"/>
+      <c r="K2478" s="1"/>
+      <c r="L2478" s="1"/>
+      <c r="M2478" s="1"/>
+      <c r="N2478" s="1"/>
+      <c r="O2478" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1295,8 +1572,12 @@
     <hyperlink ref="H4" r:id="rId18" xr:uid="{C4E0C6BA-B5C8-4F46-9BD0-107BEFD28C6A}"/>
     <hyperlink ref="H21" r:id="rId19" xr:uid="{5EC65BAA-9064-428C-A5E9-3941F6C86E3C}"/>
     <hyperlink ref="H22" r:id="rId20" xr:uid="{84A053E2-0209-425A-8A4E-B07290100CD5}"/>
+    <hyperlink ref="H23" r:id="rId21" xr:uid="{2D37A2DC-A49D-4C85-AD41-D7840407D070}"/>
+    <hyperlink ref="H24" r:id="rId22" xr:uid="{07BFD9CB-3E42-44E0-87F5-9002F7F28DA1}"/>
+    <hyperlink ref="H25" r:id="rId23" xr:uid="{4F7F8117-1F93-45A4-B4CD-87CF8B9A147B}"/>
+    <hyperlink ref="H26" r:id="rId24" xr:uid="{F0994850-B19A-41E6-95ED-E8D1FCA5CD68}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId21"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId25"/>
 </worksheet>
 </file>
--- a/reports.xlsx
+++ b/reports.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ts1\Desktop\ReportsPortal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87926D59-0272-4E9D-905B-C83E04929DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91177954-0DB0-4722-BE37-1E459B3B8486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="125">
   <si>
     <t>دمشق</t>
   </si>
@@ -44,18 +44,6 @@
     <t>Year</t>
   </si>
   <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>Governorate</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>ReportType</t>
-  </si>
-  <si>
     <t>ReportName</t>
   </si>
   <si>
@@ -288,6 +276,141 @@
   </si>
   <si>
     <t>Forecasting Feb 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المحافظة </t>
+  </si>
+  <si>
+    <t>المستحضر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القسم </t>
+  </si>
+  <si>
+    <t xml:space="preserve">نوع التقرير </t>
+  </si>
+  <si>
+    <t>تفصيل مستحضرات</t>
+  </si>
+  <si>
+    <t>تقرير أداء المبيعات – محافظة دمشق لنهاية 4</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQBFoL0ke9WORJb2Z1a7nmcvAZgQvacLEkw6_epwUFgxg5k?e=2QRPcy</t>
+  </si>
+  <si>
+    <t>اللاذقية</t>
+  </si>
+  <si>
+    <t>تقرير أداء المبيعات – محافظة اللاذقية لنهاية 4</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQAGLqTPDhL3QY3Nk9qDeXFMAU9TzUS-m0GJ5kC7zHc6h6A?e=BvzjT0</t>
+  </si>
+  <si>
+    <t>تقرير أداء المبيعات – محافظة طرطوس لنهاية 4</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQBxQ3LcB1sMQIaYUaL0lPTGAYXDiyG8jSd_EnVU8w4EROw?e=Up5xAZ</t>
+  </si>
+  <si>
+    <t>تقرير أداء تحقيق الاهداف – بيت الحكمة  لنهاية 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حماة </t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQBYwS_A5uPrQZhPJY5XXQLGAaJXml-ueowLSn2Pvc2Rcy0?e=gsfYj3</t>
+  </si>
+  <si>
+    <t>تقرير أداء تحقيق الاهداف – ادم فارما لنهاية 4</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQCV__FVswQJQa2i98sePuqEAf2yHkZ11mnU8J-PG7-qcG8?e=4CLEJe</t>
+  </si>
+  <si>
+    <t>تقرير أداء تحقيق الاهداف – الوطني لنهاية 4</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQCfWLRRx09ZQ7b5kmZg6h48ATqu17J5jUjH4hrz5dies_s?e=JqYXCB</t>
+  </si>
+  <si>
+    <t>تقرير أداء تحقيق الاهداف – امالكو لنهاية 4</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQDvXw6QGwJETrSryByLKdnFAZJgrgEM1P2MvkpnmNUoWVE?e=2hBodF</t>
+  </si>
+  <si>
+    <t>تقرير أداء تحقيق الاهداف – خضر اللاذقية لنهاية 4</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQCxCmoaJTqJQZRYU_SlhNccARR2wf8QFZCFd3DTPBmy9Hs?e=lue8MR</t>
+  </si>
+  <si>
+    <t>تقرير أداء تحقيق الاهداف – الاهلي  لنهاية 4</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQDyznRGbvFYR7NR4Cs9mUZyAfEpn2y5MNtsKgp0vdM6M7Y?e=g1g4hJ</t>
+  </si>
+  <si>
+    <t>تقرير أداء تحقيق الاهداف – شام اللاذقية  لنهاية 4</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQCaFnCPlwKOQqN7nsZBwSoQAUYWfZPSxpFk8Cyl0S4mJyc?e=Acrhw5</t>
+  </si>
+  <si>
+    <t>تقرير أداء تحقيق الاهداف – خضر طرطوس  لنهاية 4</t>
+  </si>
+  <si>
+    <t>تقرير أداء تحقيق الاهداف – البيروني طرطوس  لنهاية 4</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQBxnPaTUeUvT7aaEyVxqGBHAVyM1Cr1V6UlMOtV83bAGCk?e=Ga6SCd</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQBCLZTVCtgZRZpyyej5edWWAQmnFpriPDcxE52bf18_2iM?e=zh2DxE</t>
+  </si>
+  <si>
+    <t>تقرير أداء تحقيق الاهداف – المستقبل طرطوس  لنهاية 4</t>
+  </si>
+  <si>
+    <t>ادلب</t>
+  </si>
+  <si>
+    <t>تقرير أداء المبيعات – محافظة ادلب لنهاية 4</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQAjc-bOD-VoSL3fDELIXTE9AdTw0mQqjPUXR7vT0yktHhw?e=S0WTUm</t>
+  </si>
+  <si>
+    <t>تقرير أداء المبيعات – محافظة حلب لنهاية 4</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQBY-W5u77HLQ6zTMye5824cAauXEMPLjCZkrDIdqUBdXgI?e=65XRvf</t>
+  </si>
+  <si>
+    <t>تقرير أداء المبيعات – محافظة حماة لنهاية 4</t>
+  </si>
+  <si>
+    <t>حماة</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQDnwie_bKf0Qqtq5pcmZYYKARXUfTciR5cSvqyMJjGfcF4?e=szbRmq</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQDI7R_DX5QQRpWVd9vAH2pIATl2HAvJggkAJrXV6QuFvTw?e=7fRyyV</t>
+  </si>
+  <si>
+    <t>تقرير أداء المبيعات – محافظة حمص لنهاية 4</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQBFoL0ke9WORJb2Z1a7nmcvAZgQvacLEkw6_epwUFgxg5k?e=s8KrY7</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQCOIT2yrAXWT4UALTz5J8FNAb8LzFxv5Tt6PQ05M0sHVA0?e=1AbaGW</t>
+  </si>
+  <si>
+    <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQAGLqTPDhL3QY3Nk9qDeXFMAU9TzUS-m0GJ5kC7zHc6h6A?e=egXHFB</t>
   </si>
 </sst>
 </file>
@@ -361,7 +484,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -389,6 +512,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -671,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2478"/>
+  <dimension ref="A1:O2485"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="2" customWidth="1"/>
@@ -679,8 +811,8 @@
     <col min="3" max="3" width="19.85546875" style="2" customWidth="1"/>
     <col min="4" max="4" width="19" style="2" customWidth="1"/>
     <col min="5" max="5" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="42.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="27.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="50.5703125" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="167.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.28515625" customWidth="1"/>
     <col min="15" max="15" width="13.140625" customWidth="1"/>
@@ -691,25 +823,25 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -720,22 +852,22 @@
         <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -746,22 +878,22 @@
         <v>3</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -772,22 +904,22 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>12</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -798,22 +930,22 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>28</v>
+        <v>6</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -824,22 +956,22 @@
         <v>3</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="9" t="s">
         <v>8</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -850,22 +982,22 @@
         <v>3</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -876,22 +1008,22 @@
         <v>3</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>27</v>
+        <v>20</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -902,22 +1034,22 @@
         <v>3</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>9</v>
+        <v>20</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>5</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -928,22 +1060,22 @@
         <v>3</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -954,22 +1086,22 @@
         <v>3</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="11" t="s">
         <v>0</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -980,22 +1112,22 @@
         <v>3</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1006,22 +1138,22 @@
         <v>3</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1032,22 +1164,22 @@
         <v>3</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1058,22 +1190,22 @@
         <v>2</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1084,22 +1216,22 @@
         <v>2</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1110,22 +1242,22 @@
         <v>2025</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>48</v>
+        <v>43</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1133,25 +1265,25 @@
         <v>2026</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>47</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1159,25 +1291,25 @@
         <v>2026</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1188,22 +1320,22 @@
         <v>3</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>51</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1214,22 +1346,22 @@
         <v>3</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>65</v>
+        <v>17</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1240,22 +1372,22 @@
         <v>3</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>70</v>
+        <v>17</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>66</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1266,22 +1398,22 @@
         <v>4</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G23" t="s">
-        <v>72</v>
+        <v>70</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>68</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1292,22 +1424,22 @@
         <v>3</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D24" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G24" t="s">
-        <v>76</v>
+      <c r="G24" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1318,22 +1450,22 @@
         <v>3</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>79</v>
+        <v>73</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1344,210 +1476,599 @@
         <v>3</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="9"/>
+      <c r="A27" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B27" s="8">
+        <v>4</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="9"/>
+      <c r="A28" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B28" s="8">
+        <v>4</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="9"/>
+      <c r="A29" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B29" s="8">
+        <v>4</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="9"/>
+      <c r="A30" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B30" s="8">
+        <v>4</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="9"/>
+      <c r="A31" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B31" s="8">
+        <v>4</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="9"/>
+      <c r="A32" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B32" s="8">
+        <v>4</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="9"/>
+      <c r="A33" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B33" s="8">
+        <v>4</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="9"/>
+      <c r="A34" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B34" s="8">
+        <v>4</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="9"/>
+      <c r="A35" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B35" s="8">
+        <v>4</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="9"/>
+      <c r="A36" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B36" s="8">
+        <v>4</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="5"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="9"/>
+      <c r="A37" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B37" s="8">
+        <v>4</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="5"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="9"/>
+      <c r="A38" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B38" s="8">
+        <v>4</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F38" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="5"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="9"/>
+      <c r="A39" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B39" s="8">
+        <v>4</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="9"/>
+      <c r="A40" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B40" s="8">
+        <v>4</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F40" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
+      <c r="A41" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B41" s="8">
+        <v>4</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
+      <c r="A42" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B42" s="8">
+        <v>4</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F42" t="s">
+        <v>20</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-    </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2478" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F2478" s="3"/>
-      <c r="G2478" s="3"/>
-      <c r="H2478" s="3"/>
-      <c r="I2478" s="1"/>
-      <c r="J2478" s="1"/>
-      <c r="K2478" s="1"/>
-      <c r="L2478" s="1"/>
-      <c r="M2478" s="1"/>
-      <c r="N2478" s="1"/>
-      <c r="O2478" s="1"/>
+      <c r="A43" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B43" s="8">
+        <v>4</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B44" s="8">
+        <v>4</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B45" s="8">
+        <v>4</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B46" s="8">
+        <v>4</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46" t="s">
+        <v>20</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="5"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="9"/>
+    </row>
+    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="8"/>
+    </row>
+    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="8"/>
+    </row>
+    <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="8"/>
+    </row>
+    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2485" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F2485" s="3"/>
+      <c r="H2485" s="3"/>
+      <c r="I2485" s="1"/>
+      <c r="J2485" s="1"/>
+      <c r="K2485" s="1"/>
+      <c r="L2485" s="1"/>
+      <c r="M2485" s="1"/>
+      <c r="N2485" s="1"/>
+      <c r="O2485" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1576,8 +2097,28 @@
     <hyperlink ref="H24" r:id="rId22" xr:uid="{07BFD9CB-3E42-44E0-87F5-9002F7F28DA1}"/>
     <hyperlink ref="H25" r:id="rId23" xr:uid="{4F7F8117-1F93-45A4-B4CD-87CF8B9A147B}"/>
     <hyperlink ref="H26" r:id="rId24" xr:uid="{F0994850-B19A-41E6-95ED-E8D1FCA5CD68}"/>
+    <hyperlink ref="H27" r:id="rId25" xr:uid="{562D9443-A825-4C44-A847-3E4BDF8C91C5}"/>
+    <hyperlink ref="H28" r:id="rId26" xr:uid="{194CC452-6DFC-47F5-9001-0AD9A83EC69D}"/>
+    <hyperlink ref="H29" r:id="rId27" xr:uid="{8BAC5DBF-47DF-4B9E-B5C9-8908CF13B306}"/>
+    <hyperlink ref="H37" r:id="rId28" xr:uid="{67B001C2-2BB9-4919-B36F-B475CC9458A5}"/>
+    <hyperlink ref="H38" r:id="rId29" xr:uid="{B75C9A56-9802-4DB9-95E8-A1F9172814B0}"/>
+    <hyperlink ref="H39" r:id="rId30" xr:uid="{183F8139-7DEE-4FCC-8CFA-58FE878FB6C7}"/>
+    <hyperlink ref="H40" r:id="rId31" xr:uid="{5EFA47E0-A584-485F-84F9-D67E95C8D544}"/>
+    <hyperlink ref="H41" r:id="rId32" xr:uid="{5A63FDDF-72CB-4528-B7B0-50EB8A06C87B}"/>
+    <hyperlink ref="H42" r:id="rId33" xr:uid="{5D370D26-CDB0-4EB5-BA2B-A1A9DA4FBDA1}"/>
+    <hyperlink ref="H43" r:id="rId34" xr:uid="{80C9400B-EFAE-4E51-ABB3-9CA3BDE9CA90}"/>
+    <hyperlink ref="H44" r:id="rId35" xr:uid="{CA43F34F-BDCA-4887-954E-AD32D35C165A}"/>
+    <hyperlink ref="H45" r:id="rId36" xr:uid="{BF7E84E6-4754-4E9E-8BF6-DD01FA499208}"/>
+    <hyperlink ref="H46" r:id="rId37" xr:uid="{64B7B575-B73D-4B62-B3AA-3AF183A57A03}"/>
+    <hyperlink ref="H30" r:id="rId38" xr:uid="{B7E686BD-6C7C-4D8C-AE20-FA5D8464622E}"/>
+    <hyperlink ref="H31" r:id="rId39" xr:uid="{71A4C001-25A7-4823-9868-CC611C699E1F}"/>
+    <hyperlink ref="H32" r:id="rId40" xr:uid="{1BD6E616-E50B-45DD-BB7C-6665499CAD50}"/>
+    <hyperlink ref="H33" r:id="rId41" xr:uid="{9506A36B-E9ED-4142-B395-5A33F735D0BE}"/>
+    <hyperlink ref="H34" r:id="rId42" xr:uid="{0D518320-CE47-47A7-890B-9F32C49B6F47}"/>
+    <hyperlink ref="H35" r:id="rId43" xr:uid="{E1CAE2D2-EF59-43BF-A339-11E55E3619CE}"/>
+    <hyperlink ref="H36" r:id="rId44" xr:uid="{5B24493E-DDED-4B96-AE93-5C89747C9FEE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId25"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId45"/>
 </worksheet>
 </file>
--- a/reports.xlsx
+++ b/reports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ts1\Desktop\ReportsPortal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91177954-0DB0-4722-BE37-1E459B3B8486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2F4303-4000-4BA3-B94B-299FB09978ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="124">
   <si>
     <t>دمشق</t>
   </si>
@@ -278,18 +278,6 @@
     <t>Forecasting Feb 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">المحافظة </t>
-  </si>
-  <si>
-    <t>المستحضر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">القسم </t>
-  </si>
-  <si>
-    <t xml:space="preserve">نوع التقرير </t>
-  </si>
-  <si>
     <t>تفصيل مستحضرات</t>
   </si>
   <si>
@@ -411,6 +399,15 @@
   </si>
   <si>
     <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQAGLqTPDhL3QY3Nk9qDeXFMAU9TzUS-m0GJ5kC7zHc6h6A?e=egXHFB</t>
+  </si>
+  <si>
+    <t>products</t>
+  </si>
+  <si>
+    <t>governorates</t>
+  </si>
+  <si>
+    <t>report_types</t>
   </si>
 </sst>
 </file>
@@ -513,13 +510,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -826,16 +823,16 @@
         <v>7</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>2</v>
@@ -1502,7 +1499,7 @@
         <v>4</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>0</v>
@@ -1514,10 +1511,10 @@
         <v>20</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1528,22 +1525,22 @@
         <v>4</v>
       </c>
       <c r="C28" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F28" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>88</v>
-      </c>
       <c r="H28" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1554,7 +1551,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>10</v>
@@ -1566,10 +1563,10 @@
         <v>20</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1580,10 +1577,10 @@
         <v>4</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>4</v>
@@ -1592,10 +1589,10 @@
         <v>20</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1606,7 +1603,7 @@
         <v>4</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>5</v>
@@ -1618,10 +1615,10 @@
         <v>20</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1632,10 +1629,10 @@
         <v>4</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>4</v>
@@ -1644,10 +1641,10 @@
         <v>20</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1658,7 +1655,7 @@
         <v>4</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>28</v>
@@ -1670,10 +1667,10 @@
         <v>20</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1684,7 +1681,7 @@
         <v>4</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>0</v>
@@ -1696,10 +1693,10 @@
         <v>20</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1710,22 +1707,22 @@
         <v>4</v>
       </c>
       <c r="C35" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F35" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>88</v>
-      </c>
       <c r="H35" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1736,7 +1733,7 @@
         <v>4</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>10</v>
@@ -1748,10 +1745,10 @@
         <v>20</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1762,10 +1759,10 @@
         <v>4</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>4</v>
@@ -1774,10 +1771,10 @@
         <v>20</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1788,7 +1785,7 @@
         <v>4</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>0</v>
@@ -1800,10 +1797,10 @@
         <v>20</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1814,22 +1811,22 @@
         <v>4</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D39" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F39" t="s">
-        <v>20</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>97</v>
-      </c>
       <c r="H39" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1840,7 +1837,7 @@
         <v>4</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>0</v>
@@ -1852,10 +1849,10 @@
         <v>20</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1866,10 +1863,10 @@
         <v>4</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>4</v>
@@ -1878,10 +1875,10 @@
         <v>20</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1892,10 +1889,10 @@
         <v>4</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>4</v>
@@ -1904,10 +1901,10 @@
         <v>20</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1918,10 +1915,10 @@
         <v>4</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>4</v>
@@ -1930,10 +1927,10 @@
         <v>20</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1944,7 +1941,7 @@
         <v>4</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>10</v>
@@ -1956,10 +1953,10 @@
         <v>20</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1970,7 +1967,7 @@
         <v>4</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>10</v>
@@ -1982,10 +1979,10 @@
         <v>20</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1996,7 +1993,7 @@
         <v>4</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>10</v>
@@ -2008,10 +2005,10 @@
         <v>20</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/reports.xlsx
+++ b/reports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ts1\Desktop\ReportsPortal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2F4303-4000-4BA3-B94B-299FB09978ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D8EFCF-F432-4FAA-AFFF-FD1C50275BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="125">
   <si>
     <t>دمشق</t>
   </si>
@@ -401,13 +401,16 @@
     <t>https://ultramedicahq.sharepoint.com/:x:/s/SalesUM-TechnicalTechniquesSales/IQAGLqTPDhL3QY3Nk9qDeXFMAU9TzUS-m0GJ5kC7zHc6h6A?e=egXHFB</t>
   </si>
   <si>
-    <t>products</t>
-  </si>
-  <si>
-    <t>governorates</t>
-  </si>
-  <si>
-    <t>report_types</t>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Governorate</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>ReportType</t>
   </si>
 </sst>
 </file>
@@ -829,10 +832,10 @@
         <v>122</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>2</v>
